--- a/data/trans_dic/IP15-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP15-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..)</t>
+          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,25; 31,71</t>
+          <t>18,14; 32,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,63; 32,39</t>
+          <t>18,21; 33,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,45; 37,34</t>
+          <t>18,0; 37,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,29; 53,63</t>
+          <t>17,22; 52,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,99; 31,54</t>
+          <t>16,59; 31,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,36; 29,0</t>
+          <t>13,85; 29,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,12; 21,96</t>
+          <t>7,29; 20,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,39; 35,36</t>
+          <t>16,7; 36,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,82; 28,88</t>
+          <t>19,13; 29,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,47; 28,94</t>
+          <t>18,16; 29,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,51; 25,31</t>
+          <t>14,19; 25,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,46; 40,18</t>
+          <t>19,12; 39,72</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,41; 22,7</t>
+          <t>16,49; 22,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,72; 22,98</t>
+          <t>16,45; 22,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,84; 20,52</t>
+          <t>15,02; 20,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,54; 40,93</t>
+          <t>20,58; 39,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,7; 21,44</t>
+          <t>15,72; 21,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,45; 23,64</t>
+          <t>17,32; 23,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,84; 20,12</t>
+          <t>14,68; 20,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,73; 26,99</t>
+          <t>19,75; 27,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,93; 21,02</t>
+          <t>16,78; 21,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,07; 22,23</t>
+          <t>17,83; 22,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,93; 19,68</t>
+          <t>15,48; 19,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,41; 31,91</t>
+          <t>21,55; 31,86</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,43; 17,23</t>
+          <t>9,31; 17,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,66; 27,52</t>
+          <t>16,79; 27,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,36; 21,42</t>
+          <t>12,08; 21,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,05; 34,15</t>
+          <t>21,28; 33,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,62; 27,71</t>
+          <t>17,72; 27,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,79; 28,92</t>
+          <t>17,98; 28,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,6; 20,31</t>
+          <t>11,31; 20,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,4; 31,64</t>
+          <t>19,48; 31,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,3; 20,78</t>
+          <t>14,37; 20,85</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,91; 26,55</t>
+          <t>18,73; 26,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,96; 19,46</t>
+          <t>13,03; 19,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,56; 31,2</t>
+          <t>21,96; 31,02</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,07; 20,79</t>
+          <t>16,3; 20,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,26; 23,23</t>
+          <t>18,31; 23,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,72; 20,56</t>
+          <t>15,78; 20,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,6; 38,04</t>
+          <t>22,6; 38,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,48; 22,18</t>
+          <t>17,48; 22,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,63; 23,68</t>
+          <t>18,85; 23,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,34; 18,82</t>
+          <t>14,4; 19,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,87; 26,87</t>
+          <t>21,35; 27,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,57; 21,08</t>
+          <t>17,46; 20,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,16; 22,66</t>
+          <t>19,12; 22,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,61; 18,91</t>
+          <t>15,79; 18,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,82; 30,56</t>
+          <t>22,79; 29,94</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>22047</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23061</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15691</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15229</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>15667</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>42306</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41168</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24477</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>30897</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>16487; 29130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16821; 30979</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10687; 21995</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8811; 26841</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14404; 27706</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>11934; 25105</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4999; 14312</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>10354; 22490</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>33992; 52131</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>32422; 51849</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>18158; 33227</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>21636; 44957</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>80707</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>88236</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>82979</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>120843</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>120023</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>168376</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>189270</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>168599</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>240866</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>68610; 93635</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>74408; 103148</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>70935; 96893</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>94619; 183173</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>74991; 101290</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>85629; 116140</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>71737; 99388</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>101871; 140215</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>149832; 188551</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>168831; 210587</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>148804; 189731</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>210262; 310798</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>22551</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>36404</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28792</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>41642</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>46511</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>57817</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>75836</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>57661</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>88153</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>16204; 30235</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28001; 45936</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>20854; 37120</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>31817; 50823</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>28028; 44166</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>30699; 49106</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>21210; 37718</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>35717; 57737</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>47754; 69249</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>63224; 89028</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>46939; 69182</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>73119; 103254</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>125305</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>147701</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>127461</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>177715</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>182201</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>268498</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>306275</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>250737</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>359916</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>110980; 142532</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>130280; 167322</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>111129; 144884</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>149245; 253194</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>126171; 163076</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>141604; 178241</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>107274; 142274</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>162543; 206332</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>244929; 290609</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>279691; 334227</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>228851; 273319</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>323948; 425635</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP15-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP15-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,14; 32,06</t>
+          <t>17,66; 32,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,21; 33,54</t>
+          <t>18,5; 33,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,0; 37,04</t>
+          <t>18,2; 36,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,22; 52,45</t>
+          <t>17,4; 56,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,59; 31,9</t>
+          <t>17,0; 31,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,85; 29,13</t>
+          <t>14,21; 29,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,29; 20,86</t>
+          <t>6,36; 20,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,7; 36,27</t>
+          <t>16,45; 36,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,13; 29,33</t>
+          <t>18,24; 29,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,16; 29,04</t>
+          <t>18,54; 29,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,19; 25,96</t>
+          <t>14,06; 26,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,12; 39,72</t>
+          <t>19,5; 41,35</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,49; 22,5</t>
+          <t>16,53; 22,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,45; 22,81</t>
+          <t>16,64; 23,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,02; 20,52</t>
+          <t>14,79; 20,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,58; 39,85</t>
+          <t>20,56; 40,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,72; 21,24</t>
+          <t>15,72; 21,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,32; 23,49</t>
+          <t>17,66; 23,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,68; 20,34</t>
+          <t>14,84; 20,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,75; 27,18</t>
+          <t>19,85; 27,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,78; 21,11</t>
+          <t>16,79; 21,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,83; 22,25</t>
+          <t>18,04; 22,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,48; 19,74</t>
+          <t>15,66; 19,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,55; 31,86</t>
+          <t>21,63; 32,17</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,31; 17,37</t>
+          <t>9,24; 17,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,79; 27,54</t>
+          <t>16,7; 27,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,08; 21,49</t>
+          <t>12,77; 21,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,28; 33,98</t>
+          <t>21,83; 34,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,72; 27,93</t>
+          <t>17,35; 28,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,98; 28,76</t>
+          <t>18,27; 29,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,31; 20,12</t>
+          <t>11,26; 20,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,48; 31,49</t>
+          <t>19,81; 31,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,37; 20,85</t>
+          <t>14,17; 21,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,73; 26,38</t>
+          <t>18,77; 26,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,03; 19,21</t>
+          <t>13,29; 19,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,96; 31,02</t>
+          <t>22,37; 30,55</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,3; 20,93</t>
+          <t>16,22; 20,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,31; 23,52</t>
+          <t>18,36; 23,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,78; 20,57</t>
+          <t>15,79; 20,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,6; 38,34</t>
+          <t>22,28; 36,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,48; 22,59</t>
+          <t>17,63; 22,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,85; 23,72</t>
+          <t>18,91; 23,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,4; 19,1</t>
+          <t>14,51; 19,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,35; 27,1</t>
+          <t>21,02; 27,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,46; 20,71</t>
+          <t>17,54; 20,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,12; 22,85</t>
+          <t>19,04; 22,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,79; 18,86</t>
+          <t>15,71; 18,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,79; 29,94</t>
+          <t>22,73; 29,68</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16487; 29130</t>
+          <t>16046; 29507</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16821; 30979</t>
+          <t>17085; 30835</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10687; 21995</t>
+          <t>10804; 21634</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8811; 26841</t>
+          <t>8903; 28892</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14404; 27706</t>
+          <t>14760; 27560</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11934; 25105</t>
+          <t>12249; 25153</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4999; 14312</t>
+          <t>4365; 13887</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10354; 22490</t>
+          <t>10197; 22427</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33992; 52131</t>
+          <t>32415; 51648</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32422; 51849</t>
+          <t>33102; 52728</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18158; 33227</t>
+          <t>17997; 33423</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21636; 44957</t>
+          <t>22075; 46804</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68610; 93635</t>
+          <t>68771; 94194</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74408; 103148</t>
+          <t>75262; 104555</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70935; 96893</t>
+          <t>69872; 95968</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94619; 183173</t>
+          <t>94525; 186257</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74991; 101290</t>
+          <t>74998; 101778</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85629; 116140</t>
+          <t>87339; 118317</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71737; 99388</t>
+          <t>72523; 99795</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>101871; 140215</t>
+          <t>102390; 139545</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>149832; 188551</t>
+          <t>149986; 187636</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>168831; 210587</t>
+          <t>170822; 208705</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>148804; 189731</t>
+          <t>150491; 188253</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>210262; 310798</t>
+          <t>210981; 313897</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16204; 30235</t>
+          <t>16082; 30968</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28001; 45936</t>
+          <t>27855; 45297</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20854; 37120</t>
+          <t>22061; 37225</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31817; 50823</t>
+          <t>32648; 51385</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28028; 44166</t>
+          <t>27444; 44953</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30699; 49106</t>
+          <t>31189; 49854</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21210; 37718</t>
+          <t>21112; 37507</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35717; 57737</t>
+          <t>36318; 58385</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47754; 69249</t>
+          <t>47073; 70351</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63224; 89028</t>
+          <t>63368; 88573</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46939; 69182</t>
+          <t>47880; 71573</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>73119; 103254</t>
+          <t>74462; 101687</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>110980; 142532</t>
+          <t>110452; 142934</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>130280; 167322</t>
+          <t>130633; 166963</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>111129; 144884</t>
+          <t>111243; 143709</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>149245; 253194</t>
+          <t>147142; 241548</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>126171; 163076</t>
+          <t>127312; 160443</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>141604; 178241</t>
+          <t>142070; 176875</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>107274; 142274</t>
+          <t>108085; 141931</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>162543; 206332</t>
+          <t>160032; 206571</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>244929; 290609</t>
+          <t>246113; 294352</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>279691; 334227</t>
+          <t>278474; 331695</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>228851; 273319</t>
+          <t>227717; 273513</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>323948; 425635</t>
+          <t>323126; 421920</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP15-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP15-Estudios-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23,33%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21,01%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24,54%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>24,26%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>24,97%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>26,42%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29,76%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23,33%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,81%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,66; 32,47</t>
+          <t>16,99; 31,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,5; 33,38</t>
+          <t>14,36; 29,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,2; 36,43</t>
+          <t>7,12; 21,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,4; 56,45</t>
+          <t>15,66; 34,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,0; 31,74</t>
+          <t>17,25; 31,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,21; 29,18</t>
+          <t>17,63; 32,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 20,24</t>
+          <t>18,45; 37,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,45; 36,17</t>
+          <t>13,13; 32,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,24; 29,06</t>
+          <t>18,82; 28,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,54; 29,53</t>
+          <t>18,47; 28,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,06; 26,11</t>
+          <t>13,51; 25,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,5; 41,35</t>
+          <t>16,74; 30,44</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18,38%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20,43%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17,52%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>22,72%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>19,4%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>19,51%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>17,57%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>26,29%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>18,38%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>20,43%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,52%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,53; 22,64</t>
+          <t>15,7; 21,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,64; 23,12</t>
+          <t>17,45; 23,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,79; 20,32</t>
+          <t>14,84; 20,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,56; 40,52</t>
+          <t>19,12; 26,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,72; 21,34</t>
+          <t>16,41; 22,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,66; 23,93</t>
+          <t>16,72; 22,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,84; 20,42</t>
+          <t>14,84; 20,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,85; 27,05</t>
+          <t>18,29; 24,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,79; 21,01</t>
+          <t>16,93; 21,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,04; 22,05</t>
+          <t>18,07; 22,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,66; 19,59</t>
+          <t>15,93; 19,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,63; 32,17</t>
+          <t>19,88; 24,95</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>22,3%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23,1%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15,4%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25,6%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>12,96%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>21,82%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>16,67%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>27,84%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>22,3%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>23,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15,4%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,24; 17,79</t>
+          <t>16,62; 27,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,7; 27,15</t>
+          <t>17,79; 28,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,77; 21,55</t>
+          <t>11,6; 20,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,83; 34,36</t>
+          <t>19,39; 31,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,35; 28,43</t>
+          <t>9,43; 17,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,27; 29,2</t>
+          <t>16,66; 27,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,26; 20,0</t>
+          <t>12,36; 21,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,81; 31,84</t>
+          <t>21,37; 33,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,17; 21,18</t>
+          <t>14,3; 20,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,77; 26,24</t>
+          <t>18,91; 26,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,29; 19,87</t>
+          <t>12,96; 19,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,37; 30,55</t>
+          <t>22,28; 30,97</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19,83%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21,1%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>18,4%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>20,76%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>18,1%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26,91%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,83%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,55%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,22; 20,99</t>
+          <t>17,48; 22,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,36; 23,47</t>
+          <t>18,63; 23,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,79; 20,4</t>
+          <t>14,34; 18,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,28; 36,57</t>
+          <t>20,52; 26,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,63; 22,22</t>
+          <t>16,07; 20,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,91; 23,54</t>
+          <t>18,26; 23,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,51; 19,06</t>
+          <t>15,72; 20,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,02; 27,14</t>
+          <t>20,0; 25,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,54; 20,98</t>
+          <t>17,57; 21,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,04; 22,68</t>
+          <t>19,16; 22,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,71; 18,87</t>
+          <t>15,61; 18,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,73; 29,68</t>
+          <t>21,25; 25,33</t>
         </is>
       </c>
     </row>
@@ -1246,13 +1246,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>22047</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>23061</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15229</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18107</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16046; 29507</t>
+          <t>14755; 27394</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17085; 30835</t>
+          <t>12380; 24993</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10804; 21634</t>
+          <t>4884; 15069</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8903; 28892</t>
+          <t>8886; 19589</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14760; 27560</t>
+          <t>15677; 28815</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12249; 25153</t>
+          <t>16281; 29917</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4365; 13887</t>
+          <t>10955; 22173</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10197; 22427</t>
+          <t>6023; 14869</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32415; 51648</t>
+          <t>33454; 51329</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33102; 52728</t>
+          <t>32974; 51671</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17997; 33423</t>
+          <t>17295; 32389</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22075; 46804</t>
+          <t>17180; 31237</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>127</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>144</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>88236</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>82979</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>120023</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>240866</t>
+          <t>200597</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68771; 94194</t>
+          <t>74864; 102287</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75262; 104555</t>
+          <t>86297; 116872</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69872; 95968</t>
+          <t>72518; 98335</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94525; 186257</t>
+          <t>90853; 125249</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74998; 101778</t>
+          <t>68275; 94431</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87339; 118317</t>
+          <t>75591; 103907</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72523; 99795</t>
+          <t>70076; 96929</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>102390; 139545</t>
+          <t>78925; 106105</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>149986; 187636</t>
+          <t>151194; 187720</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>170822; 208705</t>
+          <t>171074; 210488</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>150491; 188253</t>
+          <t>153053; 189114</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>210981; 313897</t>
+          <t>180260; 226254</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>66</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>36404</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>28792</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16082; 30968</t>
+          <t>26283; 43815</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27855; 45297</t>
+          <t>30372; 49380</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22061; 37225</t>
+          <t>21752; 38076</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32648; 51385</t>
+          <t>32661; 53872</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27444; 44953</t>
+          <t>16414; 29993</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31189; 49854</t>
+          <t>27798; 45906</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21112; 37507</t>
+          <t>21346; 36987</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36318; 58385</t>
+          <t>32057; 49773</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47073; 70351</t>
+          <t>47500; 69043</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63368; 88573</t>
+          <t>63836; 89626</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47880; 71573</t>
+          <t>46690; 70103</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>74462; 101687</t>
+          <t>70945; 98607</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>192</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>226</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>110452; 142934</t>
+          <t>126191; 160127</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>130633; 166963</t>
+          <t>139959; 177942</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>111243; 143709</t>
+          <t>106791; 140198</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>147142; 241548</t>
+          <t>143688; 185319</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>127312; 160443</t>
+          <t>109450; 141613</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>142070; 176875</t>
+          <t>129929; 165279</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>108085; 141931</t>
+          <t>110759; 144834</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>160032; 206571</t>
+          <t>125497; 162084</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>246113; 294352</t>
+          <t>246565; 295760</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>278474; 331695</t>
+          <t>280199; 331488</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>227717; 273513</t>
+          <t>226261; 274110</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>323126; 421920</t>
+          <t>282084; 336288</t>
         </is>
       </c>
     </row>
